--- a/data/trans_camb/P1427-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1427-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>6,36</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; -0,65</t>
+          <t>-4,35; -0,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,91</t>
+          <t>2,44; 7,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,64</t>
+          <t>-2,74; 1,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,7</t>
+          <t>4,72; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,0</t>
+          <t>-2,78; 0,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,0</t>
+          <t>4,78; 8,07</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121,18%</t>
+          <t>102,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128,72%</t>
+          <t>116,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>126,71%</t>
+          <t>111,57%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,55; -14,16</t>
+          <t>-69,48; -10,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,9; 217,39</t>
+          <t>40,7; 181,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 31,49</t>
+          <t>-37,52; 30,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,47; 207,4</t>
+          <t>63,37; 178,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 0,79</t>
+          <t>-43,46; 1,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,55; 181,04</t>
+          <t>72,96; 161,84</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,28</t>
+          <t>-0,8; 0,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,49</t>
+          <t>0,33; 1,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,04</t>
+          <t>-0,29; 0,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,68</t>
+          <t>0,66; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,45</t>
+          <t>-0,38; 0,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,45</t>
+          <t>0,7; 1,61</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>104,73%</t>
+          <t>123,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206,54%</t>
+          <t>240,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>143,4%</t>
+          <t>167,71%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,44; 62,81</t>
+          <t>-71,07; 62,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 281,41</t>
+          <t>17,75; 306,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 417,26</t>
+          <t>-36,11; 327,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 630,93</t>
+          <t>56,06; 716,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 92,84</t>
+          <t>-39,68; 112,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,98; 303,9</t>
+          <t>63,24; 363,59</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,0</t>
+          <t>-0,94; 1,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,01</t>
+          <t>-0,1; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,84</t>
+          <t>-0,26; 1,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,03</t>
+          <t>0,54; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,14</t>
+          <t>-0,26; 1,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,05</t>
+          <t>0,58; 2,12</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>171,57%</t>
+          <t>154,02%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353,0%</t>
+          <t>380,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>248,48%</t>
+          <t>250,68%</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 968,71</t>
+          <t>-29,53; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,23; —</t>
+          <t>7,6; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 660,97</t>
+          <t>-44,74; 730,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,09; 828,65</t>
+          <t>45,27; 909,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,41</t>
+          <t>-1,65; -0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,82</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,36</t>
+          <t>-1,08; 0,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,58</t>
+          <t>0,94; 2,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; -0,17</t>
+          <t>-1,13; -0,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,98</t>
+          <t>1,0; 2,03</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,76; -21,65</t>
+          <t>-66,32; -23,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 110,75</t>
+          <t>16,28; 110,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 15,03</t>
+          <t>-35,31; 20,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,93; 113,51</t>
+          <t>29,05; 111,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,72; -7,37</t>
+          <t>-43,04; -6,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,32; 97,09</t>
+          <t>36,95; 99,26</t>
         </is>
       </c>
     </row>
